--- a/rtos-api-analysis/results/memory/FreeRTOS_memory_and_coverage_analysis.xlsx
+++ b/rtos-api-analysis/results/memory/FreeRTOS_memory_and_coverage_analysis.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,7 +461,7 @@
         <v>18022</v>
       </c>
       <c r="C2" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="D2" t="n">
         <v>0.79</v>
@@ -477,7 +477,7 @@
         <v>800</v>
       </c>
       <c r="C3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="D3" t="n">
         <v>0.77</v>
@@ -493,7 +493,7 @@
         <v>2351</v>
       </c>
       <c r="C4" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="D4" t="n">
         <v>0.12</v>
@@ -509,7 +509,7 @@
         <v>1704</v>
       </c>
       <c r="C5" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="D5" t="n">
         <v>0.82</v>
@@ -525,7 +525,7 @@
         <v>2425</v>
       </c>
       <c r="C6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="D6" t="n">
         <v>0.41</v>
@@ -538,13 +538,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23797454</v>
+        <v>8418671</v>
       </c>
       <c r="C7" t="n">
-        <v>1088.25</v>
+        <v>454.79</v>
       </c>
       <c r="D7" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="8">
@@ -557,7 +557,7 @@
         <v>1016</v>
       </c>
       <c r="C8" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="D8" t="n">
         <v>0.78</v>
@@ -573,7 +573,7 @@
         <v>665</v>
       </c>
       <c r="C9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="D9" t="n">
         <v>0.76</v>
@@ -589,7 +589,7 @@
         <v>24434</v>
       </c>
       <c r="C10" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="D10" t="n">
         <v>0.55</v>
@@ -605,7 +605,7 @@
         <v>47364</v>
       </c>
       <c r="C11" t="n">
-        <v>7.53</v>
+        <v>7.85</v>
       </c>
       <c r="D11" t="n">
         <v>0.84</v>
@@ -653,7 +653,7 @@
         <v>2332</v>
       </c>
       <c r="C14" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="D14" t="n">
         <v>0.77</v>
@@ -669,7 +669,7 @@
         <v>19689</v>
       </c>
       <c r="C15" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="D15" t="n">
         <v>0.83</v>
@@ -701,7 +701,7 @@
         <v>645</v>
       </c>
       <c r="C17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="D17" t="n">
         <v>0.76</v>
@@ -717,7 +717,7 @@
         <v>634</v>
       </c>
       <c r="C18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="D18" t="n">
         <v>0.74</v>
@@ -765,7 +765,7 @@
         <v>599</v>
       </c>
       <c r="C21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="D21" t="n">
         <v>0.75</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>560969</v>
+        <v>1003950</v>
       </c>
       <c r="C22" t="n">
-        <v>24.25</v>
+        <v>46.59</v>
       </c>
       <c r="D22" t="n">
         <v>0.6899999999999999</v>
@@ -813,7 +813,7 @@
         <v>931</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="D24" t="n">
         <v>0.78</v>
@@ -822,926 +822,926 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>xTaskCallApplicationTaskHook</t>
+          <t>test_MPU_xTaskGetTickCount</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>619</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>test_MPU_xTaskGetTickCount</t>
+          <t>test_MPU_xQueueAddToSet</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>619</v>
+        <v>851</v>
       </c>
       <c r="C26" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="D26" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueAddToSet</t>
+          <t>test_MPU_vTaskList</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>851</v>
+        <v>589</v>
       </c>
       <c r="C27" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="D27" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>test_MPU_vTaskList</t>
+          <t>test_MPU_uxEventGroupGetNumber</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>589</v>
+        <v>740</v>
       </c>
       <c r="C28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="D28" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>test_MPU_uxEventGroupGetNumber</t>
+          <t>test_MPU_vTaskDelay</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>740</v>
+        <v>10911</v>
       </c>
       <c r="C29" t="n">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="D29" t="n">
-        <v>0.77</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>test_MPU_vTaskDelay</t>
+          <t>test_MPU_xStreamBufferIsFull</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10911</v>
+        <v>1680</v>
       </c>
       <c r="C30" t="n">
-        <v>1.84</v>
+        <v>1.16</v>
       </c>
       <c r="D30" t="n">
-        <v>0.52</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>test_MPU_xStreamBufferIsFull</t>
+          <t>test_MPU_xTaskCreate</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1680</v>
+        <v>18279</v>
       </c>
       <c r="C31" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="D31" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>test_MPU_xTaskCreate</t>
+          <t>test_MPU_vTimerSetTimerID</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>18279</v>
+        <v>745</v>
       </c>
       <c r="C32" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="D32" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>test_MPU_vTimerSetTimerID</t>
+          <t>test_MPU_uxTimerGetReloadMode</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>745</v>
+        <v>835</v>
       </c>
       <c r="C33" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="D33" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>test_MPU_uxTimerGetReloadMode</t>
+          <t>test_MPU_xTaskCheckForTimeOut</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>835</v>
+        <v>1751</v>
       </c>
       <c r="C34" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="D34" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>test_MPU_xTaskCheckForTimeOut</t>
+          <t>test_MPU_xTimerCreate</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1751</v>
+        <v>1564</v>
       </c>
       <c r="C35" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>test_MPU_xTimerCreate</t>
+          <t>test_MPU_xQueueCreateCountingSemaphoreStatic</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1564</v>
+        <v>1242</v>
       </c>
       <c r="C36" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueCreateCountingSemaphoreStatic</t>
+          <t>test_MPU_vTaskSetTimeOutState</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1242</v>
+        <v>709</v>
       </c>
       <c r="C37" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="D37" t="n">
-        <v>0.43</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>test_MPU_vTaskSetTimeOutState</t>
+          <t>test_MPU_xTaskGetHandle</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>709</v>
+        <v>2092</v>
       </c>
       <c r="C38" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="D38" t="n">
-        <v>0.76</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>test_MPU_xTaskGetHandle</t>
+          <t>test_MPU_vTaskGetInfo</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2092</v>
+        <v>5371</v>
       </c>
       <c r="C39" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="D39" t="n">
-        <v>0.41</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>test_MPU_vTaskGetInfo</t>
+          <t>test_MPU_xTimerGetPeriod</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5371</v>
+        <v>705</v>
       </c>
       <c r="C40" t="n">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>test_MPU_xTimerGetPeriod</t>
+          <t>test_MPU_xQueueSelectFromSet</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>705</v>
+        <v>7928554</v>
       </c>
       <c r="C41" t="n">
-        <v>1.04</v>
+        <v>435.04</v>
       </c>
       <c r="D41" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueSelectFromSet</t>
+          <t>test_MPU_vTaskMissedYield</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>23766104</v>
+        <v>578</v>
       </c>
       <c r="C42" t="n">
-        <v>1097.3</v>
+        <v>1.02</v>
       </c>
       <c r="D42" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>test_MPU_vTaskMissedYield</t>
+          <t>test_MPU_xQueueRemoveFromSet</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>578</v>
+        <v>861</v>
       </c>
       <c r="C43" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="D43" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueRemoveFromSet</t>
+          <t>test_MPU_xStreamBufferBytesAvailable</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>861</v>
+        <v>1160</v>
       </c>
       <c r="C44" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="D44" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>test_MPU_xStreamBufferBytesAvailable</t>
+          <t>test_MPU_vEventGroupDelete</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1160</v>
+        <v>3615</v>
       </c>
       <c r="C45" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="D45" t="n">
-        <v>0.79</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>test_MPU_vEventGroupDelete</t>
+          <t>test_MPU_xQueueGenericCreate</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3615</v>
+        <v>3207</v>
       </c>
       <c r="C46" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="D46" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueGenericCreate</t>
+          <t>test_MPU_xTaskCreateStatic</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3207</v>
+        <v>7215</v>
       </c>
       <c r="C47" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="D47" t="n">
-        <v>0.67</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>test_MPU_xTaskCreateStatic</t>
+          <t>test_MPU_vTaskSetThreadLocalStoragePointer</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7215</v>
+        <v>926</v>
       </c>
       <c r="C48" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="D48" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>test_MPU_vTaskSetThreadLocalStoragePointer</t>
+          <t>test_MPU_vTaskPrioritySet</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>926</v>
+        <v>24814</v>
       </c>
       <c r="C49" t="n">
-        <v>1.14</v>
+        <v>2.48</v>
       </c>
       <c r="D49" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>test_MPU_vTaskPrioritySet</t>
+          <t>test_MPU_xEventGroupWaitBits</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>24814</v>
+        <v>193163</v>
       </c>
       <c r="C50" t="n">
-        <v>2.32</v>
+        <v>5.85</v>
       </c>
       <c r="D50" t="n">
-        <v>0.84</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>test_MPU_xEventGroupWaitBits</t>
+          <t>test_MPU_xTaskDelayUntil</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>193163</v>
+        <v>20696</v>
       </c>
       <c r="C51" t="n">
-        <v>5.41</v>
+        <v>2.33</v>
       </c>
       <c r="D51" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>test_MPU_xTaskDelayUntil</t>
+          <t>test_MPU_uxTaskGetStackHighWaterMark2</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>20696</v>
+        <v>1164</v>
       </c>
       <c r="C52" t="n">
-        <v>2.23</v>
+        <v>1.08</v>
       </c>
       <c r="D52" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>test_MPU_uxTaskGetStackHighWaterMark2</t>
+          <t>test_MPU_xTaskGenericNotifyWait</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1164</v>
+        <v>4109</v>
       </c>
       <c r="C53" t="n">
-        <v>1.08</v>
+        <v>2.07</v>
       </c>
       <c r="D53" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>test_MPU_xTaskGenericNotifyWait</t>
+          <t>test_MPU_xQueueTakeMutexRecursive</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4180</v>
+        <v>10099608</v>
       </c>
       <c r="C54" t="n">
-        <v>2.11</v>
+        <v>442.45</v>
       </c>
       <c r="D54" t="n">
-        <v>0.82</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueTakeMutexRecursive</t>
+          <t>test_MPU_vTaskStartScheduler</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>30039010</v>
+        <v>4398</v>
       </c>
       <c r="C55" t="n">
-        <v>1015.13</v>
+        <v>2.86</v>
       </c>
       <c r="D55" t="n">
-        <v>0.62</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>test_MPU_vTaskStartScheduler</t>
+          <t>test_MPU_uxTaskGetSystemState</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4398</v>
+        <v>10609</v>
       </c>
       <c r="C56" t="n">
-        <v>2.85</v>
+        <v>1.99</v>
       </c>
       <c r="D56" t="n">
-        <v>0.13</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>test_MPU_uxTaskGetSystemState</t>
+          <t>test_MPU_xTimerGenericCommand</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10609</v>
+        <v>4381845</v>
       </c>
       <c r="C57" t="n">
-        <v>1.96</v>
+        <v>302.68</v>
       </c>
       <c r="D57" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>test_MPU_xTimerGenericCommand</t>
+          <t>test_MPU_xQueueGetMutexHolder</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4381845</v>
+        <v>815</v>
       </c>
       <c r="C58" t="n">
-        <v>230.52</v>
+        <v>1.07</v>
       </c>
       <c r="D58" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueGetMutexHolder</t>
+          <t>test_MPU_eTaskGetState</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>815</v>
+        <v>1425</v>
       </c>
       <c r="C59" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="D59" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>test_MPU_eTaskGetState</t>
+          <t>test_MPU_xStreamBufferSpacesAvailable</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1425</v>
+        <v>955</v>
       </c>
       <c r="C60" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="D60" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>test_MPU_xStreamBufferSpacesAvailable</t>
+          <t>test_MPU_vTaskSuspendAll</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>955</v>
+        <v>588</v>
       </c>
       <c r="C61" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="D61" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>test_MPU_vTaskSuspendAll</t>
+          <t>test_MPU_xStreamBufferGenericCreateStatic</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>588</v>
+        <v>15656</v>
       </c>
       <c r="C62" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="D62" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>test_MPU_xStreamBufferGenericCreateStatic</t>
+          <t>test_MPU_xEventGroupCreate</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>15656</v>
+        <v>869</v>
       </c>
       <c r="C63" t="n">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="D63" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>test_MPU_xEventGroupCreate</t>
+          <t>test_MPU_xEventGroupSetBits</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>869</v>
+        <v>48918</v>
       </c>
       <c r="C64" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="D64" t="n">
-        <v>0.85</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>test_MPU_xEventGroupSetBits</t>
+          <t>test_MPU_xStreamBufferIsEmpty</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>48918</v>
+        <v>805</v>
       </c>
       <c r="C65" t="n">
-        <v>3.62</v>
+        <v>1.06</v>
       </c>
       <c r="D65" t="n">
-        <v>0.58</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>test_MPU_xStreamBufferIsEmpty</t>
+          <t>test_MPU_xTaskResumeAll</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>805</v>
+        <v>714</v>
       </c>
       <c r="C66" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="D66" t="n">
-        <v>0.78</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>test_MPU_xTaskResumeAll</t>
+          <t>test_MPU_vTimerSetReloadMode</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>714</v>
+        <v>860</v>
       </c>
       <c r="C67" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="D67" t="n">
-        <v>0.37</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>test_MPU_vTimerSetReloadMode</t>
+          <t>test_MPU_xTimerPendFunctionCall</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>860</v>
+        <v>8559690</v>
       </c>
       <c r="C68" t="n">
-        <v>1.1</v>
+        <v>459.74</v>
       </c>
       <c r="D68" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>test_MPU_xTimerPendFunctionCall</t>
+          <t>test_MPU_xTimerGetTimerDaemonTaskHandle</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>24570448</v>
+        <v>624</v>
       </c>
       <c r="C69" t="n">
-        <v>1087.05</v>
+        <v>1.02</v>
       </c>
       <c r="D69" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>test_MPU_xTimerGetTimerDaemonTaskHandle</t>
+          <t>test_MPU_xQueueGenericReset</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>624</v>
+        <v>3906</v>
       </c>
       <c r="C70" t="n">
-        <v>1.02</v>
+        <v>1.58</v>
       </c>
       <c r="D70" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueGenericReset</t>
+          <t>test_MPU_xQueueCreateMutexStatic</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3906</v>
+        <v>347364</v>
       </c>
       <c r="C71" t="n">
-        <v>1.5</v>
+        <v>29.77</v>
       </c>
       <c r="D71" t="n">
-        <v>0.86</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueCreateMutexStatic</t>
+          <t>test_MPU_xTaskCallApplicationTaskHook</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>347364</v>
+        <v>876</v>
       </c>
       <c r="C72" t="n">
-        <v>23.27</v>
+        <v>1.08</v>
       </c>
       <c r="D72" t="n">
-        <v>0.42</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>test_MPU_xTaskCallApplicationTaskHook</t>
+          <t>test_MPU_uxTaskGetStackHighWaterMark</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>1177</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>test_MPU_uxTaskGetStackHighWaterMark</t>
+          <t>test_MPU_ucQueueGetQueueType</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1177</v>
+        <v>640</v>
       </c>
       <c r="C74" t="n">
         <v>1.08</v>
       </c>
       <c r="D74" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>test_MPU_ucQueueGetQueueType</t>
+          <t>test_MPU_xQueueCreateMutex</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>640</v>
+        <v>231087</v>
       </c>
       <c r="C75" t="n">
-        <v>1.03</v>
+        <v>20.46</v>
       </c>
       <c r="D75" t="n">
-        <v>0.76</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueCreateMutex</t>
+          <t>test_MPU_ulTaskGetIdleRunTimeCounter</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>231087</v>
+        <v>609</v>
       </c>
       <c r="C76" t="n">
-        <v>16.14</v>
+        <v>1.02</v>
       </c>
       <c r="D76" t="n">
-        <v>0.51</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>test_MPU_ulTaskGetIdleRunTimeCounter</t>
+          <t>test_MPU_xQueueCreateSet</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>609</v>
+        <v>2275</v>
       </c>
       <c r="C77" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="D77" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueCreateSet</t>
+          <t>test_MPU_xQueueGiveMutexRecursive</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2275</v>
+        <v>433444</v>
       </c>
       <c r="C78" t="n">
-        <v>1.34</v>
+        <v>38.01</v>
       </c>
       <c r="D78" t="n">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueGiveMutexRecursive</t>
+          <t>test_MPU_xTimerGetExpiryTime</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>433444</v>
+        <v>735</v>
       </c>
       <c r="C79" t="n">
-        <v>27.89</v>
+        <v>1.04</v>
       </c>
       <c r="D79" t="n">
-        <v>0.46</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>test_MPU_xTimerGetExpiryTime</t>
+          <t>test_MPU_xEventGroupClearBits</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>735</v>
+        <v>996</v>
       </c>
       <c r="C80" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="D80" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>test_MPU_xEventGroupClearBits</t>
+          <t>test_MPU_vStreamBufferDelete</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>996</v>
+        <v>889</v>
       </c>
       <c r="C81" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="D81" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>test_MPU_vStreamBufferDelete</t>
+          <t>test_MPU_vQueueAddToRegistry</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>889</v>
+        <v>1393</v>
       </c>
       <c r="C82" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="D82" t="n">
         <v>0.77</v>
@@ -1750,400 +1750,384 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>test_MPU_vQueueAddToRegistry</t>
+          <t>test_MPU_xStreamBufferGenericCreate</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1393</v>
+        <v>9706</v>
       </c>
       <c r="C83" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="D83" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>test_MPU_xStreamBufferGenericCreate</t>
+          <t>test_MPU_vQueueUnregisterQueue</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>9706</v>
+        <v>1024</v>
       </c>
       <c r="C84" t="n">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="D84" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>test_MPU_vQueueUnregisterQueue</t>
+          <t>test_MPU_xTaskGetCurrentTaskHandle</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1024</v>
+        <v>619</v>
       </c>
       <c r="C85" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="D85" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>test_MPU_xTaskGetCurrentTaskHandle</t>
+          <t>test_MPU_xTaskGetIdleTaskHandle</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="C86" t="n">
         <v>1.02</v>
       </c>
       <c r="D86" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>test_MPU_xTaskGetIdleTaskHandle</t>
+          <t>test_MPU_ulTaskGenericNotifyValueClear</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>624</v>
+        <v>972</v>
       </c>
       <c r="C87" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="D87" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>test_MPU_ulTaskGenericNotifyValueClear</t>
+          <t>test_MPU_uxQueueSpacesAvailable</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>972</v>
+        <v>760</v>
       </c>
       <c r="C88" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="D88" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>test_MPU_uxQueueSpacesAvailable</t>
+          <t>test_MPU_xTaskGenericNotifyStateClear</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>760</v>
+        <v>1376</v>
       </c>
       <c r="C89" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="D89" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>test_MPU_xTaskGenericNotifyStateClear</t>
+          <t>test_MPU_xStreamBufferReset</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1376</v>
+        <v>1865</v>
       </c>
       <c r="C90" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="D90" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>test_MPU_xStreamBufferReset</t>
+          <t>test_MPU_xEventGroupSync</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1865</v>
+        <v>2484512</v>
       </c>
       <c r="C91" t="n">
-        <v>1.17</v>
+        <v>65.13</v>
       </c>
       <c r="D91" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>test_MPU_xEventGroupSync</t>
+          <t>test_MPU_xTaskCatchUpTicks</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2484512</v>
+        <v>3821</v>
       </c>
       <c r="C92" t="n">
-        <v>56.91</v>
+        <v>1.52</v>
       </c>
       <c r="D92" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>test_MPU_xTaskCatchUpTicks</t>
+          <t>test_MPU_xTaskGetApplicationTaskTag</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3821</v>
+        <v>790</v>
       </c>
       <c r="C93" t="n">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="D93" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>test_MPU_xTaskGetApplicationTaskTag</t>
+          <t>test_MPU_xQueueGenericSend</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>790</v>
+        <v>8167504</v>
       </c>
       <c r="C94" t="n">
-        <v>1.05</v>
+        <v>460.68</v>
       </c>
       <c r="D94" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueGenericSend</t>
+          <t>test_MPU_pcQueueGetName</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>23397372</v>
+        <v>1043</v>
       </c>
       <c r="C95" t="n">
-        <v>1085.59</v>
+        <v>1.07</v>
       </c>
       <c r="D95" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>test_MPU_pcQueueGetName</t>
+          <t>test_MPU_xQueueSemaphoreTake</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1043</v>
+        <v>8420111</v>
       </c>
       <c r="C96" t="n">
-        <v>1.07</v>
+        <v>454.95</v>
       </c>
       <c r="D96" t="n">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueSemaphoreTake</t>
+          <t>test_MPU_ulTaskGenericNotifyTake</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>24985888</v>
+        <v>3368</v>
       </c>
       <c r="C97" t="n">
-        <v>1043.79</v>
+        <v>1.99</v>
       </c>
       <c r="D97" t="n">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>test_MPU_ulTaskGenericNotifyTake</t>
+          <t>test_MPU_vTaskSetApplicationTaskTag</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>3336</v>
+        <v>770</v>
       </c>
       <c r="C98" t="n">
-        <v>1.94</v>
+        <v>1.05</v>
       </c>
       <c r="D98" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>test_MPU_vTaskSetApplicationTaskTag</t>
+          <t>test_MPU_xQueueCreateCountingSemaphore</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>770</v>
+        <v>2361</v>
       </c>
       <c r="C99" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="D99" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueCreateCountingSemaphore</t>
+          <t>test_MPU_xQueueGenericCreateStatic</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2361</v>
+        <v>3639</v>
       </c>
       <c r="C100" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="D100" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueGenericCreateStatic</t>
+          <t>test_MPU_pvTimerGetTimerID</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3639</v>
+        <v>740</v>
       </c>
       <c r="C101" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="D101" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>test_MPU_pvTimerGetTimerID</t>
+          <t>test_MPU_xQueueReceive</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>740</v>
+        <v>8270250</v>
       </c>
       <c r="C102" t="n">
-        <v>1.05</v>
+        <v>447.54</v>
       </c>
       <c r="D102" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>test_MPU_xQueueReceive</t>
+          <t>test_MPU_xStreamBufferNextMessageLengthBytes</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>23775985</v>
+        <v>5595</v>
       </c>
       <c r="C103" t="n">
-        <v>1087.08</v>
+        <v>1.5</v>
       </c>
       <c r="D103" t="n">
-        <v>0.68</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>test_MPU_xStreamBufferNextMessageLengthBytes</t>
+          <t>test_MPU_vQueueDelete</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5595</v>
+        <v>1302</v>
       </c>
       <c r="C104" t="n">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="D104" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>test_MPU_vQueueDelete</t>
+          <t>test_MPU_xStreamBufferSend</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1302</v>
+        <v>27881</v>
       </c>
       <c r="C105" t="n">
-        <v>1.09</v>
+        <v>2.86</v>
       </c>
       <c r="D105" t="n">
-        <v>0.78</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>test_MPU_xStreamBufferSend</t>
+          <t>test_MPU_vTaskGetRunTimeStats</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>27881</v>
+        <v>589</v>
       </c>
       <c r="C106" t="n">
-        <v>2.7</v>
+        <v>1.02</v>
       </c>
       <c r="D106" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>test_MPU_vTaskGetRunTimeStats</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>589</v>
-      </c>
-      <c r="C107" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="D107" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -2215,34 +2199,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8015.33</v>
+        <v>3791.9</v>
       </c>
       <c r="B2" t="n">
-        <v>75.6163</v>
+        <v>36.1133</v>
       </c>
       <c r="C2" t="n">
-        <v>1097.3</v>
+        <v>460.68</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>267.3145</v>
+        <v>115.4771</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6947</v>
+        <v>0.7073</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0189</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0.86</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>

--- a/rtos-api-analysis/results/memory/FreeRTOS_memory_and_coverage_analysis.xlsx
+++ b/rtos-api-analysis/results/memory/FreeRTOS_memory_and_coverage_analysis.xlsx
@@ -461,7 +461,7 @@
         <v>18022</v>
       </c>
       <c r="C2" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="D2" t="n">
         <v>0.79</v>
@@ -477,7 +477,7 @@
         <v>800</v>
       </c>
       <c r="C3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="D3" t="n">
         <v>0.77</v>
@@ -493,7 +493,7 @@
         <v>2351</v>
       </c>
       <c r="C4" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="D4" t="n">
         <v>0.12</v>
@@ -509,7 +509,7 @@
         <v>1704</v>
       </c>
       <c r="C5" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="D5" t="n">
         <v>0.82</v>
@@ -525,7 +525,7 @@
         <v>2425</v>
       </c>
       <c r="C6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="D6" t="n">
         <v>0.41</v>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8418671</v>
+        <v>12112748</v>
       </c>
       <c r="C7" t="n">
-        <v>454.79</v>
+        <v>508.25</v>
       </c>
       <c r="D7" t="n">
         <v>0.66</v>
@@ -557,7 +557,7 @@
         <v>1016</v>
       </c>
       <c r="C8" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="D8" t="n">
         <v>0.78</v>
@@ -573,7 +573,7 @@
         <v>665</v>
       </c>
       <c r="C9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="D9" t="n">
         <v>0.76</v>
@@ -589,7 +589,7 @@
         <v>24434</v>
       </c>
       <c r="C10" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="D10" t="n">
         <v>0.55</v>
@@ -605,7 +605,7 @@
         <v>47364</v>
       </c>
       <c r="C11" t="n">
-        <v>7.85</v>
+        <v>7.55</v>
       </c>
       <c r="D11" t="n">
         <v>0.84</v>
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2332</v>
+        <v>1972030</v>
       </c>
       <c r="C14" t="n">
-        <v>1.34</v>
+        <v>360.59</v>
       </c>
       <c r="D14" t="n">
-        <v>0.77</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="15">
@@ -669,7 +669,7 @@
         <v>19689</v>
       </c>
       <c r="C15" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="D15" t="n">
         <v>0.83</v>
@@ -701,7 +701,7 @@
         <v>645</v>
       </c>
       <c r="C17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="D17" t="n">
         <v>0.76</v>
@@ -717,7 +717,7 @@
         <v>634</v>
       </c>
       <c r="C18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="D18" t="n">
         <v>0.74</v>
@@ -765,7 +765,7 @@
         <v>599</v>
       </c>
       <c r="C21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="D21" t="n">
         <v>0.75</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1003950</v>
+        <v>1026905</v>
       </c>
       <c r="C22" t="n">
-        <v>46.59</v>
+        <v>41.18</v>
       </c>
       <c r="D22" t="n">
         <v>0.6899999999999999</v>
@@ -813,7 +813,7 @@
         <v>931</v>
       </c>
       <c r="C24" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="D24" t="n">
         <v>0.78</v>
@@ -829,7 +829,7 @@
         <v>619</v>
       </c>
       <c r="C25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="D25" t="n">
         <v>0.76</v>
@@ -861,7 +861,7 @@
         <v>589</v>
       </c>
       <c r="C27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="D27" t="n">
         <v>0.75</v>
@@ -893,7 +893,7 @@
         <v>10911</v>
       </c>
       <c r="C29" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="D29" t="n">
         <v>0.52</v>
@@ -925,7 +925,7 @@
         <v>18279</v>
       </c>
       <c r="C31" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="D31" t="n">
         <v>0.79</v>
@@ -941,7 +941,7 @@
         <v>745</v>
       </c>
       <c r="C32" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="D32" t="n">
         <v>0.77</v>
@@ -989,7 +989,7 @@
         <v>1564</v>
       </c>
       <c r="C35" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="D35" t="n">
         <v>0.4</v>
@@ -1005,7 +1005,7 @@
         <v>1242</v>
       </c>
       <c r="C36" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="D36" t="n">
         <v>0.43</v>
@@ -1037,7 +1037,7 @@
         <v>2092</v>
       </c>
       <c r="C38" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="D38" t="n">
         <v>0.41</v>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5371</v>
+        <v>6119</v>
       </c>
       <c r="C39" t="n">
         <v>1.64</v>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7928554</v>
+        <v>13473156</v>
       </c>
       <c r="C41" t="n">
-        <v>435.04</v>
+        <v>579.61</v>
       </c>
       <c r="D41" t="n">
         <v>0.66</v>
@@ -1101,7 +1101,7 @@
         <v>578</v>
       </c>
       <c r="C42" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="D42" t="n">
         <v>0.75</v>
@@ -1117,7 +1117,7 @@
         <v>861</v>
       </c>
       <c r="C43" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="D43" t="n">
         <v>0.78</v>
@@ -1133,7 +1133,7 @@
         <v>1160</v>
       </c>
       <c r="C44" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="D44" t="n">
         <v>0.79</v>
@@ -1146,13 +1146,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3615</v>
+        <v>7841</v>
       </c>
       <c r="C45" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="D45" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="46">
@@ -1165,7 +1165,7 @@
         <v>3207</v>
       </c>
       <c r="C46" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="D46" t="n">
         <v>0.67</v>
@@ -1197,7 +1197,7 @@
         <v>926</v>
       </c>
       <c r="C48" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="D48" t="n">
         <v>0.78</v>
@@ -1213,7 +1213,7 @@
         <v>24814</v>
       </c>
       <c r="C49" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="D49" t="n">
         <v>0.84</v>
@@ -1229,7 +1229,7 @@
         <v>193163</v>
       </c>
       <c r="C50" t="n">
-        <v>5.85</v>
+        <v>5.35</v>
       </c>
       <c r="D50" t="n">
         <v>0.63</v>
@@ -1245,7 +1245,7 @@
         <v>20696</v>
       </c>
       <c r="C51" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="D51" t="n">
         <v>0.55</v>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1164</v>
+        <v>1234</v>
       </c>
       <c r="C52" t="n">
         <v>1.08</v>
@@ -1277,7 +1277,7 @@
         <v>4109</v>
       </c>
       <c r="C53" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="D53" t="n">
         <v>0.82</v>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10099608</v>
+        <v>13620222</v>
       </c>
       <c r="C54" t="n">
-        <v>442.45</v>
+        <v>462.96</v>
       </c>
       <c r="D54" t="n">
         <v>0.6</v>
@@ -1309,7 +1309,7 @@
         <v>4398</v>
       </c>
       <c r="C55" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="D55" t="n">
         <v>0.13</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10609</v>
+        <v>15396</v>
       </c>
       <c r="C56" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="D56" t="n">
         <v>0.53</v>
@@ -1341,7 +1341,7 @@
         <v>4381845</v>
       </c>
       <c r="C57" t="n">
-        <v>302.68</v>
+        <v>230.36</v>
       </c>
       <c r="D57" t="n">
         <v>0.5</v>
@@ -1357,7 +1357,7 @@
         <v>815</v>
       </c>
       <c r="C58" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="D58" t="n">
         <v>0.78</v>
@@ -1389,7 +1389,7 @@
         <v>955</v>
       </c>
       <c r="C60" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="D60" t="n">
         <v>0.79</v>
@@ -1405,7 +1405,7 @@
         <v>588</v>
       </c>
       <c r="C61" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="D61" t="n">
         <v>0.75</v>
@@ -1421,7 +1421,7 @@
         <v>15656</v>
       </c>
       <c r="C62" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="D62" t="n">
         <v>0.83</v>
@@ -1453,7 +1453,7 @@
         <v>48918</v>
       </c>
       <c r="C64" t="n">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="D64" t="n">
         <v>0.58</v>
@@ -1485,7 +1485,7 @@
         <v>714</v>
       </c>
       <c r="C66" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="D66" t="n">
         <v>0.37</v>
@@ -1501,7 +1501,7 @@
         <v>860</v>
       </c>
       <c r="C67" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="D67" t="n">
         <v>0.78</v>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>8559690</v>
+        <v>12327364</v>
       </c>
       <c r="C68" t="n">
-        <v>459.74</v>
+        <v>511.14</v>
       </c>
       <c r="D68" t="n">
         <v>0.68</v>
@@ -1549,7 +1549,7 @@
         <v>3906</v>
       </c>
       <c r="C70" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="D70" t="n">
         <v>0.86</v>
@@ -1565,7 +1565,7 @@
         <v>347364</v>
       </c>
       <c r="C71" t="n">
-        <v>29.77</v>
+        <v>23.27</v>
       </c>
       <c r="D71" t="n">
         <v>0.42</v>
@@ -1581,7 +1581,7 @@
         <v>876</v>
       </c>
       <c r="C72" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="D72" t="n">
         <v>0.77</v>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1177</v>
+        <v>1254</v>
       </c>
       <c r="C73" t="n">
         <v>1.08</v>
@@ -1613,7 +1613,7 @@
         <v>640</v>
       </c>
       <c r="C74" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="D74" t="n">
         <v>0.76</v>
@@ -1629,7 +1629,7 @@
         <v>231087</v>
       </c>
       <c r="C75" t="n">
-        <v>20.46</v>
+        <v>16.13</v>
       </c>
       <c r="D75" t="n">
         <v>0.51</v>
@@ -1661,7 +1661,7 @@
         <v>2275</v>
       </c>
       <c r="C77" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="D77" t="n">
         <v>0.66</v>
@@ -1677,7 +1677,7 @@
         <v>433444</v>
       </c>
       <c r="C78" t="n">
-        <v>38.01</v>
+        <v>27.89</v>
       </c>
       <c r="D78" t="n">
         <v>0.46</v>
@@ -1709,7 +1709,7 @@
         <v>996</v>
       </c>
       <c r="C80" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="D80" t="n">
         <v>0.78</v>
@@ -1725,7 +1725,7 @@
         <v>889</v>
       </c>
       <c r="C81" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="D81" t="n">
         <v>0.77</v>
@@ -1741,7 +1741,7 @@
         <v>1393</v>
       </c>
       <c r="C82" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="D82" t="n">
         <v>0.77</v>
@@ -1757,7 +1757,7 @@
         <v>9706</v>
       </c>
       <c r="C83" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="D83" t="n">
         <v>0.83</v>
@@ -1773,7 +1773,7 @@
         <v>1024</v>
       </c>
       <c r="C84" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="D84" t="n">
         <v>0.78</v>
@@ -1837,7 +1837,7 @@
         <v>760</v>
       </c>
       <c r="C88" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="D88" t="n">
         <v>0.77</v>
@@ -1853,7 +1853,7 @@
         <v>1376</v>
       </c>
       <c r="C89" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="D89" t="n">
         <v>0.79</v>
@@ -1869,7 +1869,7 @@
         <v>1865</v>
       </c>
       <c r="C90" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="D90" t="n">
         <v>0.8100000000000001</v>
@@ -1885,7 +1885,7 @@
         <v>2484512</v>
       </c>
       <c r="C91" t="n">
-        <v>65.13</v>
+        <v>56.82</v>
       </c>
       <c r="D91" t="n">
         <v>0.68</v>
@@ -1898,13 +1898,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3821</v>
+        <v>1961483</v>
       </c>
       <c r="C92" t="n">
-        <v>1.52</v>
+        <v>359.04</v>
       </c>
       <c r="D92" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="93">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>8167504</v>
+        <v>11707458</v>
       </c>
       <c r="C94" t="n">
-        <v>460.68</v>
+        <v>509.13</v>
       </c>
       <c r="D94" t="n">
         <v>0.67</v>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>8420111</v>
+        <v>12095643</v>
       </c>
       <c r="C96" t="n">
-        <v>454.95</v>
+        <v>507.94</v>
       </c>
       <c r="D96" t="n">
         <v>0.6</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3368</v>
+        <v>3384</v>
       </c>
       <c r="C97" t="n">
         <v>1.99</v>
@@ -1997,7 +1997,7 @@
         <v>770</v>
       </c>
       <c r="C98" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="D98" t="n">
         <v>0.77</v>
@@ -2013,7 +2013,7 @@
         <v>2361</v>
       </c>
       <c r="C99" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="D99" t="n">
         <v>0.67</v>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>8270250</v>
+        <v>12962505</v>
       </c>
       <c r="C102" t="n">
-        <v>447.54</v>
+        <v>542.64</v>
       </c>
       <c r="D102" t="n">
         <v>0.66</v>
@@ -2077,7 +2077,7 @@
         <v>5595</v>
       </c>
       <c r="C103" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="D103" t="n">
         <v>0.84</v>
@@ -2093,7 +2093,7 @@
         <v>1302</v>
       </c>
       <c r="C104" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="D104" t="n">
         <v>0.78</v>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>27881</v>
+        <v>33237</v>
       </c>
       <c r="C105" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="D105" t="n">
         <v>0.6899999999999999</v>
@@ -2125,7 +2125,7 @@
         <v>589</v>
       </c>
       <c r="C106" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="D106" t="n">
         <v>0.75</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3791.9</v>
+        <v>4865.83</v>
       </c>
       <c r="B2" t="n">
-        <v>36.1133</v>
+        <v>46.3412</v>
       </c>
       <c r="C2" t="n">
-        <v>460.68</v>
+        <v>579.61</v>
       </c>
       <c r="D2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="E2" t="n">
-        <v>115.4771</v>
+        <v>137.7991</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7073</v>
+        <v>0.7047</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
